--- a/friends-with-hands/HateSpeech.xlsx
+++ b/friends-with-hands/HateSpeech.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Godot\FriendsWithHands\friends-with-hands\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BDD31F3-364D-4605-8130-4CD005E08EA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,14 +24,74 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+  <si>
+    <t>No</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Content</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Are you sleeping?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A chicken plays better than you with their peak.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>This is not how we humans in the 21 century should play.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Good job :) Well play :) You are so great :)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I think you will do better by hitting the keyborad randomly.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wow, just wow.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>You are really bad, do you know that?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maybe you should consider to do something else.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I'm sorry, did I hurt you?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boo!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -330,10 +396,154 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" customWidth="1"/>
+    <col min="2" max="2" width="53.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/friends-with-hands/HateSpeech.xlsx
+++ b/friends-with-hands/HateSpeech.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Godot\FriendsWithHands\friends-with-hands\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BDD31F3-364D-4605-8130-4CD005E08EA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{725B8639-12F7-44D5-A8EC-08806FC3B832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="3276" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
